--- a/models/MajiSafi_FINANCIAL_SOURCE_OF_TRUTH.xlsx
+++ b/models/MajiSafi_FINANCIAL_SOURCE_OF_TRUTH.xlsx
@@ -28,6 +28,8 @@
     <sheet name="CASH 13-WEEK" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="GAPS" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="CHECKS" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="REQUEST REGISTER" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="CANONICAL FIGURES" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,7 +47,7 @@
     <numFmt numFmtId="169" formatCode="0.0&quot;d&quot;"/>
     <numFmt numFmtId="170" formatCode="dd-mmm"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,6 +76,11 @@
     <font>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFC00000"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="8">
@@ -131,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -167,6 +174,9 @@
     <xf numFmtId="170" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6660,6 +6670,1273 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>REQUEST REGISTER — the Finance Desk queue</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Every request to finance, from a human or an agent. Intake: finance@maji-safi.com. Answers use LEAD. Nothing is answered twice, two different ways.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Needed by</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>Answer — L line</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>Recorded in</t>
+        </is>
+      </c>
+      <c r="K4" s="11" t="inlineStr">
+        <is>
+          <t>SLA met</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FD-001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Capital Brief (agent)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FY2025 and FY2026 statements prepared for a lender, not just URA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>The statements do not exist and nobody keeps the books. They are hygiene, not the capital asset — the October close on 10 Nov is. Appoint an accountant this week and establish the year-end.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>requests/FD-001.md</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FD-002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Capital Brief (agent)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Per-site cost: USD 80,000 or USD 20,000? 4x spread, blocks Wednesday</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>DISPUTED</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Cannot certify either until the 80,000 is decomposed. Embargoed from all outbound. Send me the build-up and I rule in a day.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>requests/FD-002.md</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FD-003</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Capital Brief (agent)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>approval</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>May impact claims built on UNBS certification be used?</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>EMBARGOED</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>No. Embargoed until the certificate is verified filed. The plant spec is still sayable; certification and anything derived from it is not.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>requests/FD-003.md</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>SLA — figure: same day (it is a lookup against canon). approval: same day. document: 3 working days or a committed date. decision: next 08:30 Ema sync or Monday cash roll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>If a deadline will be missed: 'I don't know yet. I will have that by Thursday at noon.' Commit to a time and deliver. Never bluff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Worked daily against the FINANCE-DESK label, and again every Monday after the cash roll.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CANONICAL FIGURES — the authority list</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>IF A FIGURE IS NOT HERE WITH STATUS APPROVED, IT MAY NOT LEAVE THE BUILDING. No agent, no person, no document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Mirrored for agents as knowledge-base/05-finance-desk/canonical-figures.yaml. This tab is authoritative; if they disagree, the YAML is a bug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>As-of</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Note / why blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>The 2026 capital ask</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Five locations by 31 December 2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="F6" s="32" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sammy</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>The headline ask is approved. The PER-SITE figure underneath it is not — see cost_per_site_usd. You may say "USD 400,000 for five locations". You may NOT break that into a per-site number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>All-in cost per site</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>DISPUTED</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Finance Desk</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Two sources disagree by 4x. The capital file states USD 80,000 all-in per site; the operations file states about USD 20,000 all-in and says that is the number to use with funders. Neither can be certified until the 80,000 is decomposed into plant-and-install versus fully-loaded site. Tracked as FD-002. Blocked by GAP-13 and GAP-16 (cost of sales and overheads are blended figures).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UNBS certification status</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>EMBARGOED</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sammy</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Reads VERIFY in the capital tracker and is not confirmed filed. It gates every impact and quality claim we could make. Do not state or imply certification, and do not use any impact number derived from it. Tracked as FD-003 and GAP-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Statutory financial year-end</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sammy</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Not established. Company incorporated October 2024. Until this is known we cannot say which periods FY2025 and FY2026 cover, whether statutory accounts are overdue with URA, or whether FY2026 statements can exist before the December lender deadline. Top blocking item. Tracked as FD-001.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Full break-even, including the jar programme (month 1)</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>577</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>jars/day</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(fixed opex 8,163,542 + salaries 2,575,000 + depreciation 5,250,000 + jar programme 8,250,000) / contribution 1,616.82 per unit / 26 days
+</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F10" s="32" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Finance Desk</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Planned month-1 output is 500/day, so the plan opens 77/day BELOW break-even.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cash break-even, including the jar programme (month 1)</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>452</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>jars/day</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Excludes depreciation</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Finance Desk</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FY1 net revenue — PLAN</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>1807859712</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>UGX</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Year-1 model, net of VAT and excise per IFRS 15</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F12" s="32" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Finance Desk</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>This is a FORECAST for a company that has not traded. It must always be stated as a plan, never as a result. Nothing may be described as revenue before 1 Oct 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FY1 lowest cash point — PLAN</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>17548449</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>UGX</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Month 1 of the Year-1 model</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F13" s="32" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Finance Desk</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>No facility, overdraft or committed tranche sits behind this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Customer deposits owed at month 12 — PLAN</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>157038750</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>UGX</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cumulative jar deposits received, no returns modelled</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Finance Desk</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Customers' money, repayable on jar return. Never present it as equity, headroom, distributable profit, or available as security to a lender.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Minimum cash floor — policy</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>UGX</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Finance Desk policy</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Finance Desk</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Internal policy. Below this the alarm fires and something gets cut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Plant and equipment at cost</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>315000000</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>UGX</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Year-1 model opening balance sheet</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Finance Desk</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Already paid for. No Year-1 capex is modelled — see GAP-11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Trading status</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>pre-trading until 2026-10-01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Confirmed by founder</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sammy</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Say this plainly and early. Every financial figure before 1 Oct 2026 is a forecast. A funder who discovers it themselves has found a surprise; a funder told up front has been given a fact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FY2025 and FY2026 statutory financial statements</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="F18" s="33" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sammy</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Nobody currently keeps the books. These statements appear never to have been prepared. Do not promise them to any lender or funder with a date until an accountant is appointed and the year-end is established. Tracked as FD-001.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED — use it, and quote the as-of date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>DISPUTED — two sources disagree and the Finance Desk has not ruled. Do not use it anywhere, internal or external.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>UNVERIFIED — not usable externally. Internally, mark it [UNVERIFIED].</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>EMBARGOED — do not use it, and do not use anything derived from it. The reason is recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Authority granted by Sammy Ghedamu, founder, 21 September 2026, after a 4x spread on the headline ask sat live in two files during a week when eight funders were emailed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/models/MajiSafi_FINANCIAL_SOURCE_OF_TRUTH.xlsx
+++ b/models/MajiSafi_FINANCIAL_SOURCE_OF_TRUTH.xlsx
@@ -1,35 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="START HERE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SETUP" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CHART OF ACCOUNTS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="COST BOOK" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="PRICE BOOK" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="JOURNAL" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="MONTHLY" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="BUDGET" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="P&amp;L" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TvA" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="BALANCE SHEET" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="VIEW · CO-FOUNDERS" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="VIEW · INVESTORS" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="VIEW · INTERNAL" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="VIEW · TAX (URA)" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="VIEW · LENDERS" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="VIEW · GROWTH" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="ACCESS" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="CASH 13-WEEK" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="GAPS" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="CHECKS" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="REQUEST REGISTER" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="CANONICAL FIGURES" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SETUP" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHART OF ACCOUNTS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COST BOOK" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRICE BOOK" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JOURNAL" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MONTHLY" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUDGET" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TvA" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BALANCE SHEET" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIEW · CO-FOUNDERS" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIEW · INVESTORS" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIEW · INTERNAL" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIEW · TAX (URA)" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIEW · LENDERS" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIEW · GROWTH" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACCESS" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CASH 13-WEEK" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GAPS" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHECKS" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REQUEST REGISTER" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CANONICAL FIGURES" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7373,8 +7373,10 @@
           <t>The 2026 capital ask</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
-        <v>400000</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -7383,27 +7385,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Five locations by 31 December 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="F6" s="32" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>DISPUTED</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sammy</t>
+          <t>Finance Desk</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>The headline ask is approved. The PER-SITE figure underneath it is not — see cost_per_site_usd. You may say "USD 400,000 for five locations". You may NOT break that into a per-site number.</t>
+          <t>Was APPROVED at USD 400,000 (five locations) on 21 Sep 2026. On ~1 Oct 2026 an agent desk re-based it to USD 100,000 and it went into outbound documents without founder or partner confirmation. The founder's own 2 Oct note (site 2 by March 2027, site 3 by May 2027) contradicts the five-sites-by-Q1-2027 basis of both figures. Per-site cost is itself DISPUTED (FD-002). Neither number may go outbound until the partners confirm one. Raised in "Maji Safi: Cash and Controls, October 2026" as decision 3.</t>
         </is>
       </c>
     </row>
@@ -7457,7 +7459,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>certified</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7467,17 +7469,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Confirmed by the founder, 5 Oct 2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>EMBARGOED</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F8" s="32" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7487,7 +7489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reads VERIFY in the capital tracker and is not confirmed filed. It gates every impact and quality claim we could make. Do not state or imply certification, and do not use any impact number derived from it. Tracked as FD-003 and GAP-06.</t>
+          <t>Founder confirmed certification on 5 Oct 2026. Add the certificate number and issue date here when filed, so any funder who checks gets the reference.</t>
         </is>
       </c>
     </row>
